--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmahajan\Documents\eps-us\InputData\trans\VSbS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/trans/VSbS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69E91793-1818-4D44-889A-A4ABF3FC1BF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7C4D67-74A1-4BF9-A001-F474636F2E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1331,9 +1331,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1371,7 +1371,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1477,7 +1477,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1619,7 +1619,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4757,16 +4757,13 @@
         <v>5.5878521842202787E-3</v>
       </c>
       <c r="D2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <f>'Table MV-1'!M10/'Table MV-1'!$M$61</f>
@@ -4786,16 +4783,13 @@
         <v>8.5645956308639404E-3</v>
       </c>
       <c r="D3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <f>'Table MV-1'!M11/'Table MV-1'!$M$61</f>
@@ -4815,16 +4809,13 @@
         <v>8.4314569052797456E-3</v>
       </c>
       <c r="D4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <f>'Table MV-1'!M12/'Table MV-1'!$M$61</f>
@@ -4844,16 +4835,13 @@
         <v>1.1966588141313841E-2</v>
       </c>
       <c r="D5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <f>'Table MV-1'!M13/'Table MV-1'!$M$61</f>
@@ -4873,16 +4861,13 @@
         <v>0.10017993599405446</v>
       </c>
       <c r="D6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <f>'Table MV-1'!M14/'Table MV-1'!$M$61</f>
@@ -4902,16 +4887,13 @@
         <v>1.3631815783695276E-2</v>
       </c>
       <c r="D7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <f>'Table MV-1'!M15/'Table MV-1'!$M$61</f>
@@ -4931,16 +4913,13 @@
         <v>1.169732997240849E-2</v>
       </c>
       <c r="D8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <f>'Table MV-1'!M16/'Table MV-1'!$M$61</f>
@@ -4960,16 +4939,13 @@
         <v>3.8341965823090428E-3</v>
       </c>
       <c r="D9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <f>'Table MV-1'!M17/'Table MV-1'!$M$61</f>
@@ -4989,16 +4965,13 @@
         <v>5.1000080479378894E-3</v>
       </c>
       <c r="D10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <f>'Table MV-1'!M18/'Table MV-1'!$M$61</f>
@@ -5018,16 +4991,13 @@
         <v>5.9786242795356839E-2</v>
       </c>
       <c r="D11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <f>'Table MV-1'!M19/'Table MV-1'!$M$61</f>
@@ -5047,16 +5017,13 @@
         <v>3.6664815309761158E-2</v>
       </c>
       <c r="D12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <f>'Table MV-1'!M20/'Table MV-1'!$M$61</f>
@@ -5076,16 +5043,13 @@
         <v>2.8664568903761568E-3</v>
       </c>
       <c r="D13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <f>'Table MV-1'!M21/'Table MV-1'!$M$61</f>
@@ -5105,16 +5069,13 @@
         <v>3.782530808201743E-3</v>
       </c>
       <c r="D14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <f>'Table MV-1'!M22/'Table MV-1'!$M$61</f>
@@ -5134,16 +5095,13 @@
         <v>3.2598122743969261E-2</v>
       </c>
       <c r="D15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <f>'Table MV-1'!M23/'Table MV-1'!$M$61</f>
@@ -5163,16 +5121,13 @@
         <v>2.0735859723449008E-2</v>
       </c>
       <c r="D16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <f>'Table MV-1'!M24/'Table MV-1'!$M$61</f>
@@ -5192,16 +5147,13 @@
         <v>9.1140412670434948E-3</v>
       </c>
       <c r="D17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <f>'Table MV-1'!M25/'Table MV-1'!$M$61</f>
@@ -5221,16 +5173,13 @@
         <v>6.5585725938901249E-3</v>
       </c>
       <c r="D18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <f>'Table MV-1'!M26/'Table MV-1'!$M$61</f>
@@ -5250,16 +5199,13 @@
         <v>1.0917375497904058E-2</v>
       </c>
       <c r="D19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <f>'Table MV-1'!M27/'Table MV-1'!$M$61</f>
@@ -5279,16 +5225,13 @@
         <v>2.9889643893651965E-2</v>
       </c>
       <c r="D20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <f>'Table MV-1'!M28/'Table MV-1'!$M$61</f>
@@ -5308,16 +5251,13 @@
         <v>4.5932860326547567E-3</v>
       </c>
       <c r="D21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <f>'Table MV-1'!M29/'Table MV-1'!$M$61</f>
@@ -5337,16 +5277,13 @@
         <v>2.2395125930356523E-2</v>
       </c>
       <c r="D22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <f>'Table MV-1'!M30/'Table MV-1'!$M$61</f>
@@ -5366,16 +5303,13 @@
         <v>1.3663610106222844E-2</v>
       </c>
       <c r="D23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <f>'Table MV-1'!M31/'Table MV-1'!$M$61</f>
@@ -5395,16 +5329,13 @@
         <v>8.8845260012976063E-3</v>
       </c>
       <c r="D24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <f>'Table MV-1'!M32/'Table MV-1'!$M$61</f>
@@ -5424,16 +5355,13 @@
         <v>1.9068644935909602E-2</v>
       </c>
       <c r="D25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <f>'Table MV-1'!M33/'Table MV-1'!$M$61</f>
@@ -5453,16 +5381,13 @@
         <v>7.3385270683945557E-3</v>
       </c>
       <c r="D26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <f>'Table MV-1'!M34/'Table MV-1'!$M$61</f>
@@ -5482,16 +5407,13 @@
         <v>3.3533074540795592E-2</v>
       </c>
       <c r="D27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <f>'Table MV-1'!M35/'Table MV-1'!$M$61</f>
@@ -5511,16 +5433,13 @@
         <v>5.1616095478350553E-3</v>
       </c>
       <c r="D28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <f>'Table MV-1'!M36/'Table MV-1'!$M$61</f>
@@ -5540,16 +5459,13 @@
         <v>1.7177876318098223E-2</v>
       </c>
       <c r="D29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <f>'Table MV-1'!M37/'Table MV-1'!$M$61</f>
@@ -5569,16 +5485,13 @@
         <v>3.1883744059677944E-3</v>
       </c>
       <c r="D30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <f>'Table MV-1'!M38/'Table MV-1'!$M$61</f>
@@ -5598,16 +5511,13 @@
         <v>3.0602035432785312E-3</v>
       </c>
       <c r="D31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <f>'Table MV-1'!M39/'Table MV-1'!$M$61</f>
@@ -5627,16 +5537,13 @@
         <v>2.5791157005332504E-2</v>
       </c>
       <c r="D32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <f>'Table MV-1'!M40/'Table MV-1'!$M$61</f>
@@ -5656,16 +5563,13 @@
         <v>9.7280691208571756E-3</v>
       </c>
       <c r="D33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <f>'Table MV-1'!M41/'Table MV-1'!$M$61</f>
@@ -5685,16 +5589,13 @@
         <v>8.1156995396778245E-2</v>
       </c>
       <c r="D34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <f>'Table MV-1'!M42/'Table MV-1'!$M$61</f>
@@ -5714,16 +5615,13 @@
         <v>3.311776120277922E-2</v>
       </c>
       <c r="D35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <f>'Table MV-1'!M43/'Table MV-1'!$M$61</f>
@@ -5743,16 +5641,13 @@
         <v>3.6394563568276817E-3</v>
       </c>
       <c r="D36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <f>'Table MV-1'!M44/'Table MV-1'!$M$61</f>
@@ -5772,16 +5667,13 @@
         <v>4.1215377721519487E-2</v>
       </c>
       <c r="D37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <f>'Table MV-1'!M45/'Table MV-1'!$M$61</f>
@@ -5801,16 +5693,13 @@
         <v>2.8227396969007492E-3</v>
       </c>
       <c r="D38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <f>'Table MV-1'!M46/'Table MV-1'!$M$61</f>
@@ -5830,16 +5719,13 @@
         <v>1.772632838169879E-2</v>
       </c>
       <c r="D39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <f>'Table MV-1'!M47/'Table MV-1'!$M$61</f>
@@ -5859,16 +5745,13 @@
         <v>5.4911775722848888E-2</v>
       </c>
       <c r="D40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <f>'Table MV-1'!M48/'Table MV-1'!$M$61</f>
@@ -5888,16 +5771,13 @@
         <v>2.3031012380907907E-3</v>
       </c>
       <c r="D41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <f>'Table MV-1'!M49/'Table MV-1'!$M$61</f>
@@ -5917,16 +5797,13 @@
         <v>1.6360166085592303E-2</v>
       </c>
       <c r="D42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <f>'Table MV-1'!M50/'Table MV-1'!$M$61</f>
@@ -5946,16 +5823,13 @@
         <v>2.6518452133150647E-3</v>
       </c>
       <c r="D43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <f>'Table MV-1'!M51/'Table MV-1'!$M$61</f>
@@ -5975,16 +5849,13 @@
         <v>2.9370005434842007E-2</v>
       </c>
       <c r="D44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <f>'Table MV-1'!M52/'Table MV-1'!$M$61</f>
@@ -6004,16 +5875,13 @@
         <v>7.0475096600093989E-2</v>
       </c>
       <c r="D45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <f>'Table MV-1'!M53/'Table MV-1'!$M$61</f>
@@ -6033,16 +5901,13 @@
         <v>6.3797295296725487E-3</v>
       </c>
       <c r="D46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <f>'Table MV-1'!M54/'Table MV-1'!$M$61</f>
@@ -6062,16 +5927,13 @@
         <v>1.0720648127264725E-3</v>
       </c>
       <c r="D47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="G47">
         <f>'Table MV-1'!M55/'Table MV-1'!$M$61</f>
@@ -6091,16 +5953,13 @@
         <v>3.5235064368599529E-2</v>
       </c>
       <c r="D48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <f>'Table MV-1'!M56/'Table MV-1'!$M$61</f>
@@ -6120,16 +5979,13 @@
         <v>2.4016636379262549E-2</v>
       </c>
       <c r="D49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <f>'Table MV-1'!M57/'Table MV-1'!$M$61</f>
@@ -6149,16 +6005,13 @@
         <v>3.1347214867025212E-3</v>
       </c>
       <c r="D50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <f>'Table MV-1'!M58/'Table MV-1'!$M$61</f>
@@ -6178,16 +6031,13 @@
         <v>1.4844967902637837E-2</v>
       </c>
       <c r="D51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <f>'Table MV-1'!M59/'Table MV-1'!$M$61</f>
@@ -6207,16 +6057,13 @@
         <v>4.0746411464237849E-3</v>
       </c>
       <c r="D52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <f>'Table MV-1'!M60/'Table MV-1'!$M$61</f>
@@ -6484,16 +6331,13 @@
         <v>1.9600927701391289E-2</v>
       </c>
       <c r="D2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="F2">
-        <f>'Table MV-1'!$P10/'Table MV-1'!$P$61</f>
-        <v>1.9282655873447636E-2</v>
+        <v>0</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -6512,16 +6356,13 @@
         <v>3.6314972397001131E-3</v>
       </c>
       <c r="D3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <f>'Table MV-1'!$P11/'Table MV-1'!$P$61</f>
-        <v>2.8734612685508815E-3</v>
+        <v>0</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -6540,16 +6381,13 @@
         <v>2.1767409304149131E-2</v>
       </c>
       <c r="D4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="F4">
-        <f>'Table MV-1'!$P12/'Table MV-1'!$P$61</f>
-        <v>2.194088643887716E-2</v>
+        <v>0</v>
       </c>
       <c r="G4">
         <v>0</v>
@@ -6568,16 +6406,13 @@
         <v>1.1515440266444459E-2</v>
       </c>
       <c r="D5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <f>'Table MV-1'!$P13/'Table MV-1'!$P$61</f>
-        <v>1.0559004097364129E-2</v>
+        <v>0</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -6596,16 +6431,13 @@
         <v>9.483573703336938E-2</v>
       </c>
       <c r="D6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <f>'Table MV-1'!$P14/'Table MV-1'!$P$61</f>
-        <v>0.1101732172422014</v>
+        <v>0</v>
       </c>
       <c r="G6">
         <v>0</v>
@@ -6624,16 +6456,13 @@
         <v>2.17963420575671E-2</v>
       </c>
       <c r="D7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <f>'Table MV-1'!$P15/'Table MV-1'!$P$61</f>
-        <v>1.9392719458399887E-2</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -6652,16 +6481,13 @@
         <v>9.6855101995915252E-3</v>
       </c>
       <c r="D8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="F8">
-        <f>'Table MV-1'!$P16/'Table MV-1'!$P$61</f>
-        <v>1.0392955521738887E-2</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>
@@ -6680,16 +6506,13 @@
         <v>3.607073808587494E-3</v>
       </c>
       <c r="D9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="F9">
-        <f>'Table MV-1'!$P17/'Table MV-1'!$P$61</f>
-        <v>3.6465629954535311E-3</v>
+        <v>0</v>
       </c>
       <c r="G9">
         <v>0</v>
@@ -6708,16 +6531,13 @@
         <v>8.5193982126037439E-4</v>
       </c>
       <c r="D10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="F10">
-        <f>'Table MV-1'!$P18/'Table MV-1'!$P$61</f>
-        <v>1.2922069411262062E-3</v>
+        <v>0</v>
       </c>
       <c r="G10">
         <v>0</v>
@@ -6736,16 +6556,13 @@
         <v>6.1586335732623156E-2</v>
       </c>
       <c r="D11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="F11">
-        <f>'Table MV-1'!$P19/'Table MV-1'!$P$61</f>
-        <v>6.6921421388709962E-2</v>
+        <v>0</v>
       </c>
       <c r="G11">
         <v>0</v>
@@ -6764,16 +6581,13 @@
         <v>3.1525712849526988E-2</v>
       </c>
       <c r="D12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="F12">
-        <f>'Table MV-1'!$P20/'Table MV-1'!$P$61</f>
-        <v>3.2001349757641386E-2</v>
+        <v>0</v>
       </c>
       <c r="G12">
         <v>0</v>
@@ -6792,16 +6606,13 @@
         <v>4.5222742187277015E-3</v>
       </c>
       <c r="D13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="F13">
-        <f>'Table MV-1'!$P21/'Table MV-1'!$P$61</f>
-        <v>4.5120524608973367E-3</v>
+        <v>0</v>
       </c>
       <c r="G13">
         <v>0</v>
@@ -6820,16 +6631,13 @@
         <v>7.8435139790973586E-3</v>
       </c>
       <c r="D14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="F14">
-        <f>'Table MV-1'!$P22/'Table MV-1'!$P$61</f>
-        <v>6.9502899565489131E-3</v>
+        <v>0</v>
       </c>
       <c r="G14">
         <v>0</v>
@@ -6848,16 +6656,13 @@
         <v>3.7864302450454933E-2</v>
       </c>
       <c r="D15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <f>'Table MV-1'!$P23/'Table MV-1'!$P$61</f>
-        <v>3.837338547117259E-2</v>
+        <v>0</v>
       </c>
       <c r="G15">
         <v>0</v>
@@ -6876,16 +6681,13 @@
         <v>2.3819250059067168E-2</v>
       </c>
       <c r="D16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="F16">
-        <f>'Table MV-1'!$P24/'Table MV-1'!$P$61</f>
-        <v>2.2470473208938503E-2</v>
+        <v>0</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -6904,16 +6706,13 @@
         <v>1.5005240724472678E-2</v>
       </c>
       <c r="D17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="F17">
-        <f>'Table MV-1'!$P25/'Table MV-1'!$P$61</f>
-        <v>1.3726141018743511E-2</v>
+        <v>0</v>
       </c>
       <c r="G17">
         <v>0</v>
@@ -6932,16 +6731,13 @@
         <v>1.0017236512864749E-2</v>
       </c>
       <c r="D18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="F18">
-        <f>'Table MV-1'!$P26/'Table MV-1'!$P$61</f>
-        <v>9.4360931295224514E-3</v>
+        <v>0</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -6960,16 +6756,13 @@
         <v>1.6767766333459132E-2</v>
       </c>
       <c r="D19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <f>'Table MV-1'!$P27/'Table MV-1'!$P$61</f>
-        <v>1.6163360078298817E-2</v>
+        <v>0</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -6988,16 +6781,13 @@
         <v>1.4952243799136747E-2</v>
       </c>
       <c r="D20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="F20">
-        <f>'Table MV-1'!$P28/'Table MV-1'!$P$61</f>
-        <v>1.3994268785299344E-2</v>
+        <v>0</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -7016,16 +6806,13 @@
         <v>4.472553985012004E-3</v>
       </c>
       <c r="D21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <f>'Table MV-1'!$P29/'Table MV-1'!$P$61</f>
-        <v>4.0632555805939817E-3</v>
+        <v>0</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -7044,16 +6831,13 @@
         <v>1.3953713838208291E-2</v>
       </c>
       <c r="D22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="F22">
-        <f>'Table MV-1'!$P30/'Table MV-1'!$P$61</f>
-        <v>1.5263410504658027E-2</v>
+        <v>0</v>
       </c>
       <c r="G22">
         <v>0</v>
@@ -7072,16 +6856,13 @@
         <v>1.7847984402303698E-2</v>
       </c>
       <c r="D23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="F23">
-        <f>'Table MV-1'!$P31/'Table MV-1'!$P$61</f>
-        <v>1.8254600811341285E-2</v>
+        <v>0</v>
       </c>
       <c r="G23">
         <v>0</v>
@@ -7100,16 +6881,13 @@
         <v>3.4161287854521931E-2</v>
       </c>
       <c r="D24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="F24">
-        <f>'Table MV-1'!$P32/'Table MV-1'!$P$61</f>
-        <v>3.0637308640614442E-2</v>
+        <v>0</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -7128,16 +6906,13 @@
         <v>2.221147844524117E-2</v>
       </c>
       <c r="D25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <f>'Table MV-1'!$P33/'Table MV-1'!$P$61</f>
-        <v>2.0625139489048872E-2</v>
+        <v>0</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -7156,16 +6931,13 @@
         <v>7.63482155174601E-3</v>
       </c>
       <c r="D26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="F26">
-        <f>'Table MV-1'!$P34/'Table MV-1'!$P$61</f>
-        <v>7.462400218225123E-3</v>
+        <v>0</v>
       </c>
       <c r="G26">
         <v>0</v>
@@ -7184,16 +6956,13 @@
         <v>2.1277992980917738E-2</v>
       </c>
       <c r="D27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <f>'Table MV-1'!$P35/'Table MV-1'!$P$61</f>
-        <v>2.024919884507027E-2</v>
+        <v>0</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -7212,16 +6981,13 @@
         <v>7.0185743445526595E-3</v>
       </c>
       <c r="D28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="E28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="F28">
-        <f>'Table MV-1'!$P36/'Table MV-1'!$P$61</f>
-        <v>7.0766920109744495E-3</v>
+        <v>0</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -7240,16 +7006,13 @@
         <v>7.6979830346411097E-3</v>
       </c>
       <c r="D29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="F29">
-        <f>'Table MV-1'!$P37/'Table MV-1'!$P$61</f>
-        <v>7.0143680710759082E-3</v>
+        <v>0</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -7268,16 +7031,13 @@
         <v>8.9770758442244206E-3</v>
       </c>
       <c r="D30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="F30">
-        <f>'Table MV-1'!$P38/'Table MV-1'!$P$61</f>
-        <v>9.2397053063459945E-3</v>
+        <v>0</v>
       </c>
       <c r="G30">
         <v>0</v>
@@ -7296,16 +7056,13 @@
         <v>5.0478518381385203E-3</v>
       </c>
       <c r="D31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="F31">
-        <f>'Table MV-1'!$P39/'Table MV-1'!$P$61</f>
-        <v>4.9201517649550101E-3</v>
+        <v>0</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -7324,16 +7081,13 @@
         <v>2.0550771847319699E-2</v>
       </c>
       <c r="D32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <f>'Table MV-1'!$P40/'Table MV-1'!$P$61</f>
-        <v>2.1768607643858712E-2</v>
+        <v>0</v>
       </c>
       <c r="G32">
         <v>0</v>
@@ -7352,16 +7106,13 @@
         <v>6.7792148090505171E-3</v>
       </c>
       <c r="D33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="F33">
-        <f>'Table MV-1'!$P41/'Table MV-1'!$P$61</f>
-        <v>6.4627236423600801E-3</v>
+        <v>0</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -7380,16 +7131,13 @@
         <v>4.1040438660927506E-2</v>
       </c>
       <c r="D34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="F34">
-        <f>'Table MV-1'!$P42/'Table MV-1'!$P$61</f>
-        <v>4.1044623748877983E-2</v>
+        <v>0</v>
       </c>
       <c r="G34">
         <v>0</v>
@@ -7408,16 +7156,13 @@
         <v>3.1700275653385936E-2</v>
       </c>
       <c r="D35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="F35">
-        <f>'Table MV-1'!$P43/'Table MV-1'!$P$61</f>
-        <v>3.167401497304749E-2</v>
+        <v>0</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -7436,16 +7181,13 @@
         <v>3.986117035446643E-3</v>
       </c>
       <c r="D36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="F36">
-        <f>'Table MV-1'!$P44/'Table MV-1'!$P$61</f>
-        <v>3.2585714617236724E-3</v>
+        <v>0</v>
       </c>
       <c r="G36">
         <v>0</v>
@@ -7464,16 +7206,13 @@
         <v>3.6683925395789657E-2</v>
       </c>
       <c r="D37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="F37">
-        <f>'Table MV-1'!$P45/'Table MV-1'!$P$61</f>
-        <v>3.8390028384176433E-2</v>
+        <v>0</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -7492,16 +7231,13 @@
         <v>1.4677986568760525E-2</v>
       </c>
       <c r="D38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="F38">
-        <f>'Table MV-1'!$P46/'Table MV-1'!$P$61</f>
-        <v>1.3519637696831486E-2</v>
+        <v>0</v>
       </c>
       <c r="G38">
         <v>0</v>
@@ -7520,16 +7256,13 @@
         <v>1.5566676127984676E-2</v>
       </c>
       <c r="D39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="F39">
-        <f>'Table MV-1'!$P47/'Table MV-1'!$P$61</f>
-        <v>1.4843224067571648E-2</v>
+        <v>0</v>
       </c>
       <c r="G39">
         <v>0</v>
@@ -7548,16 +7281,13 @@
         <v>3.8593803021701831E-2</v>
       </c>
       <c r="D40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <f>'Table MV-1'!$P48/'Table MV-1'!$P$61</f>
-        <v>3.8744741340554098E-2</v>
+        <v>0</v>
       </c>
       <c r="G40">
         <v>0</v>
@@ -7576,16 +7306,13 @@
         <v>2.8426879307146095E-3</v>
       </c>
       <c r="D41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="F41">
-        <f>'Table MV-1'!$P49/'Table MV-1'!$P$61</f>
-        <v>3.1409330317849157E-3</v>
+        <v>0</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -7604,16 +7331,13 @@
         <v>1.6494772704388254E-2</v>
       </c>
       <c r="D42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="F42">
-        <f>'Table MV-1'!$P50/'Table MV-1'!$P$61</f>
-        <v>1.6531642517752781E-2</v>
+        <v>0</v>
       </c>
       <c r="G42">
         <v>0</v>
@@ -7632,16 +7356,13 @@
         <v>5.1835093488657516E-3</v>
       </c>
       <c r="D43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <f>'Table MV-1'!$P51/'Table MV-1'!$P$61</f>
-        <v>4.6909021621169989E-3</v>
+        <v>0</v>
       </c>
       <c r="G43">
         <v>0</v>
@@ -7660,16 +7381,13 @@
         <v>2.1883288976798098E-2</v>
       </c>
       <c r="D44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="F44">
-        <f>'Table MV-1'!$P52/'Table MV-1'!$P$61</f>
-        <v>2.1221790819698876E-2</v>
+        <v>0</v>
       </c>
       <c r="G44">
         <v>0</v>
@@ -7688,16 +7406,13 @@
         <v>8.6297781225124395E-2</v>
       </c>
       <c r="D45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="F45">
-        <f>'Table MV-1'!$P53/'Table MV-1'!$P$61</f>
-        <v>8.1255579629910979E-2</v>
+        <v>0</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -7716,16 +7431,13 @@
         <v>8.9600234207263124E-3</v>
       </c>
       <c r="D46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="F46">
-        <f>'Table MV-1'!$P54/'Table MV-1'!$P$61</f>
-        <v>8.9868975731671758E-3</v>
+        <v>0</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -7744,16 +7456,13 @@
         <v>2.3814053188992734E-3</v>
       </c>
       <c r="D47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <f>'Table MV-1'!$P55/'Table MV-1'!$P$61</f>
-        <v>2.2031925927497274E-3</v>
+        <v>0</v>
       </c>
       <c r="G47">
         <v>0</v>
@@ -7772,16 +7481,13 @@
         <v>2.6816184066770478E-2</v>
       </c>
       <c r="D48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="F48">
-        <f>'Table MV-1'!$P56/'Table MV-1'!$P$61</f>
-        <v>2.7568275022629669E-2</v>
+        <v>0</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -7800,16 +7506,13 @@
         <v>2.6086002141878541E-2</v>
       </c>
       <c r="D49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="F49">
-        <f>'Table MV-1'!$P57/'Table MV-1'!$P$61</f>
-        <v>2.6303199799000584E-2</v>
+        <v>0</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -7828,16 +7531,13 @@
         <v>6.8260176103406393E-3</v>
       </c>
       <c r="D50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="F50">
-        <f>'Table MV-1'!$P58/'Table MV-1'!$P$61</f>
-        <v>6.0068230796770363E-3</v>
+        <v>0</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -7856,16 +7556,13 @@
         <v>2.1205726135675299E-2</v>
       </c>
       <c r="D51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="F51">
-        <f>'Table MV-1'!$P59/'Table MV-1'!$P$61</f>
-        <v>2.035520680727616E-2</v>
+        <v>0</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -7884,16 +7581,13 @@
         <v>3.9463197884523288E-3</v>
       </c>
       <c r="D52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <f>'Table MV-1'!$P60/'Table MV-1'!$P$61</f>
-        <v>3.1206476693976084E-3</v>
+        <v>0</v>
       </c>
       <c r="G52">
         <v>0</v>
@@ -8109,4 +7803,184 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
+    <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="10" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="11" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{486479BA-9C82-45F5-BBDB-D421DBACC914}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE45BD7-ED0B-409C-A575-E37A6B341E54}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51AC19AA-12F7-4F25-8EDB-0507AFD1E7C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
+++ b/InputData/trans/VSbS/Vehicle Shares by Subregion.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://energyinnovation.sharepoint.com/sites/IndiaEPS/Shared Documents/Completed EPS Variables/trans/VSbS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rachel Goldstein\Desktop\EPS Models\India EPS\InputData\trans\VSbS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C7C4D67-74A1-4BF9-A001-F474636F2E27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F00003-1487-45E8-B5E6-9461BEB31C81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="11370" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
+    <workbookView xWindow="1536" yWindow="1536" windowWidth="19188" windowHeight="11208" activeTab="3" xr2:uid="{F34BB550-7D2B-439D-9C81-D72ED5B29ABD}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="157">
   <si>
     <t>VSbS Vehicle Shares by Subregion</t>
   </si>
@@ -307,12 +307,6 @@
     <t>motorbikes</t>
   </si>
   <si>
-    <t>Massachusetts</t>
-  </si>
-  <si>
-    <t>District of Columbia</t>
-  </si>
-  <si>
     <t>Unit: dimensionless (share of vehicles)</t>
   </si>
   <si>
@@ -380,6 +374,159 @@
   </si>
   <si>
     <t>U.S. Data Notes</t>
+  </si>
+  <si>
+    <t>subregion1</t>
+  </si>
+  <si>
+    <t>subregion2</t>
+  </si>
+  <si>
+    <t>subregion3</t>
+  </si>
+  <si>
+    <t>subregion4</t>
+  </si>
+  <si>
+    <t>subregion5</t>
+  </si>
+  <si>
+    <t>subregion6</t>
+  </si>
+  <si>
+    <t>subregion7</t>
+  </si>
+  <si>
+    <t>subregion8</t>
+  </si>
+  <si>
+    <t>subregion9</t>
+  </si>
+  <si>
+    <t>subregion10</t>
+  </si>
+  <si>
+    <t>subregion11</t>
+  </si>
+  <si>
+    <t>subregion12</t>
+  </si>
+  <si>
+    <t>subregion13</t>
+  </si>
+  <si>
+    <t>subregion14</t>
+  </si>
+  <si>
+    <t>subregion15</t>
+  </si>
+  <si>
+    <t>subregion16</t>
+  </si>
+  <si>
+    <t>subregion17</t>
+  </si>
+  <si>
+    <t>subregion18</t>
+  </si>
+  <si>
+    <t>subregion19</t>
+  </si>
+  <si>
+    <t>subregion20</t>
+  </si>
+  <si>
+    <t>subregion21</t>
+  </si>
+  <si>
+    <t>subregion22</t>
+  </si>
+  <si>
+    <t>subregion23</t>
+  </si>
+  <si>
+    <t>subregion24</t>
+  </si>
+  <si>
+    <t>subregion25</t>
+  </si>
+  <si>
+    <t>subregion26</t>
+  </si>
+  <si>
+    <t>subregion27</t>
+  </si>
+  <si>
+    <t>subregion28</t>
+  </si>
+  <si>
+    <t>subregion29</t>
+  </si>
+  <si>
+    <t>subregion30</t>
+  </si>
+  <si>
+    <t>subregion31</t>
+  </si>
+  <si>
+    <t>subregion32</t>
+  </si>
+  <si>
+    <t>subregion33</t>
+  </si>
+  <si>
+    <t>subregion34</t>
+  </si>
+  <si>
+    <t>subregion35</t>
+  </si>
+  <si>
+    <t>subregion36</t>
+  </si>
+  <si>
+    <t>subregion37</t>
+  </si>
+  <si>
+    <t>subregion38</t>
+  </si>
+  <si>
+    <t>subregion39</t>
+  </si>
+  <si>
+    <t>subregion40</t>
+  </si>
+  <si>
+    <t>subregion41</t>
+  </si>
+  <si>
+    <t>subregion42</t>
+  </si>
+  <si>
+    <t>subregion43</t>
+  </si>
+  <si>
+    <t>subregion44</t>
+  </si>
+  <si>
+    <t>subregion45</t>
+  </si>
+  <si>
+    <t>subregion46</t>
+  </si>
+  <si>
+    <t>subregion47</t>
+  </si>
+  <si>
+    <t>subregion48</t>
+  </si>
+  <si>
+    <t>subregion49</t>
+  </si>
+  <si>
+    <t>subregion50</t>
+  </si>
+  <si>
+    <t>subregion51</t>
   </si>
 </sst>
 </file>
@@ -1628,9 +1775,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30B0F8C0-DE1A-4000-9351-A11EE8CD5BC4}">
   <dimension ref="A1:B26"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="70.140625" customWidth="1"/>
+    <col min="2" max="2" width="70.109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1668,22 +1815,22 @@
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13" s="102" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="B13" s="103"/>
     </row>
@@ -1692,48 +1839,48 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="23" spans="1:2">
       <c r="A23" s="100" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="B23" s="101"/>
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1748,14 +1895,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{949F6402-DD66-4CAC-8910-748EA4AEB83B}">
   <dimension ref="A1:P63"/>
-  <sheetFormatPr defaultRowHeight="8.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="7.8"/>
   <cols>
-    <col min="1" max="1" width="11.28515625" style="4" customWidth="1"/>
-    <col min="2" max="16" width="9.85546875" style="4" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="4"/>
+    <col min="1" max="1" width="11.33203125" style="4" customWidth="1"/>
+    <col min="2" max="16" width="9.88671875" style="4" customWidth="1"/>
+    <col min="17" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15">
+    <row r="1" spans="1:16" ht="13.8">
       <c r="A1" s="105" t="s">
         <v>76</v>
       </c>
@@ -1793,7 +1940,7 @@
       <c r="O2" s="96"/>
       <c r="P2" s="96"/>
     </row>
-    <row r="3" spans="1:16" ht="9">
+    <row r="3" spans="1:16" ht="9.6">
       <c r="A3" s="97" t="s">
         <v>75</v>
       </c>
@@ -1835,7 +1982,7 @@
       <c r="O4" s="107"/>
       <c r="P4" s="108"/>
     </row>
-    <row r="5" spans="1:16" ht="9">
+    <row r="5" spans="1:16" ht="9.6">
       <c r="A5" s="79"/>
       <c r="B5" s="109" t="s">
         <v>73</v>
@@ -1863,7 +2010,7 @@
       <c r="O5" s="110"/>
       <c r="P5" s="113"/>
     </row>
-    <row r="6" spans="1:16" ht="9">
+    <row r="6" spans="1:16" ht="9.6">
       <c r="A6" s="79" t="s">
         <v>68</v>
       </c>
@@ -1891,7 +2038,7 @@
       <c r="O6" s="88"/>
       <c r="P6" s="87"/>
     </row>
-    <row r="7" spans="1:16" ht="9">
+    <row r="7" spans="1:16" ht="9.6">
       <c r="A7" s="79"/>
       <c r="B7" s="79" t="s">
         <v>63</v>
@@ -1937,7 +2084,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="9">
+    <row r="8" spans="1:16" ht="9.6">
       <c r="A8" s="79"/>
       <c r="B8" s="79" t="s">
         <v>65</v>
@@ -1985,7 +2132,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="9" spans="1:16" ht="9">
+    <row r="9" spans="1:16" ht="9.6">
       <c r="A9" s="74"/>
       <c r="B9" s="74" t="s">
         <v>60</v>
@@ -2025,7 +2172,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="10" spans="1:16" ht="9">
+    <row r="10" spans="1:16" ht="9.6">
       <c r="A10" s="19" t="s">
         <v>58</v>
       </c>
@@ -2075,7 +2222,7 @@
         <v>5320340</v>
       </c>
     </row>
-    <row r="11" spans="1:16" ht="9">
+    <row r="11" spans="1:16" ht="9.6">
       <c r="A11" s="19" t="s">
         <v>57</v>
       </c>
@@ -2125,7 +2272,7 @@
         <v>792826</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="9">
+    <row r="12" spans="1:16" ht="9.6">
       <c r="A12" s="19" t="s">
         <v>56</v>
       </c>
@@ -2175,7 +2322,7 @@
         <v>6053781</v>
       </c>
     </row>
-    <row r="13" spans="1:16" ht="9">
+    <row r="13" spans="1:16" ht="9.6">
       <c r="A13" s="19" t="s">
         <v>55</v>
       </c>
@@ -2225,7 +2372,7 @@
         <v>2913369</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="9">
+    <row r="14" spans="1:16" ht="9.6">
       <c r="A14" s="52" t="s">
         <v>54</v>
       </c>
@@ -2275,7 +2422,7 @@
         <v>30398249</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="9">
+    <row r="15" spans="1:16" ht="9.6">
       <c r="A15" s="19" t="s">
         <v>53</v>
       </c>
@@ -2325,7 +2472,7 @@
         <v>5350708</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="9">
+    <row r="16" spans="1:16" ht="9.6">
       <c r="A16" s="19" t="s">
         <v>52</v>
       </c>
@@ -2375,7 +2522,7 @@
         <v>2867554</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="9">
+    <row r="17" spans="1:16" ht="9.6">
       <c r="A17" s="43" t="s">
         <v>51</v>
       </c>
@@ -2425,7 +2572,7 @@
         <v>1006135</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="9">
+    <row r="18" spans="1:16" ht="9.6">
       <c r="A18" s="19" t="s">
         <v>50</v>
       </c>
@@ -2475,7 +2622,7 @@
         <v>356537</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="9">
+    <row r="19" spans="1:16" ht="9.6">
       <c r="A19" s="19" t="s">
         <v>49</v>
       </c>
@@ -2525,7 +2672,7 @@
         <v>18464506</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="9">
+    <row r="20" spans="1:16" ht="9.6">
       <c r="A20" s="19" t="s">
         <v>48</v>
       </c>
@@ -2575,7 +2722,7 @@
         <v>8829596</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="9">
+    <row r="21" spans="1:16" ht="9.6">
       <c r="A21" s="19" t="s">
         <v>47</v>
       </c>
@@ -2625,7 +2772,7 @@
         <v>1244935</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="9">
+    <row r="22" spans="1:16" ht="9.6">
       <c r="A22" s="52" t="s">
         <v>46</v>
       </c>
@@ -2675,7 +2822,7 @@
         <v>1917677</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="9">
+    <row r="23" spans="1:16" ht="9.6">
       <c r="A23" s="19" t="s">
         <v>45</v>
       </c>
@@ -2725,7 +2872,7 @@
         <v>10587725</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="9">
+    <row r="24" spans="1:16" ht="9.6">
       <c r="A24" s="19" t="s">
         <v>44</v>
       </c>
@@ -2775,7 +2922,7 @@
         <v>6199901</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="9">
+    <row r="25" spans="1:16" ht="9.6">
       <c r="A25" s="43" t="s">
         <v>43</v>
       </c>
@@ -2825,7 +2972,7 @@
         <v>3787224</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="9">
+    <row r="26" spans="1:16" ht="9.6">
       <c r="A26" s="19" t="s">
         <v>42</v>
       </c>
@@ -2875,7 +3022,7 @@
         <v>2603543</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="9">
+    <row r="27" spans="1:16" ht="9.6">
       <c r="A27" s="19" t="s">
         <v>41</v>
       </c>
@@ -2925,7 +3072,7 @@
         <v>4459685</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="9">
+    <row r="28" spans="1:16" ht="9.6">
       <c r="A28" s="19" t="s">
         <v>40</v>
       </c>
@@ -2975,7 +3122,7 @@
         <v>3861204</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="9">
+    <row r="29" spans="1:16" ht="9.6">
       <c r="A29" s="19" t="s">
         <v>39</v>
       </c>
@@ -3025,7 +3172,7 @@
         <v>1121106</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="9">
+    <row r="30" spans="1:16" ht="9.6">
       <c r="A30" s="52" t="s">
         <v>38</v>
       </c>
@@ -3075,7 +3222,7 @@
         <v>4211377</v>
       </c>
     </row>
-    <row r="31" spans="1:16" ht="9">
+    <row r="31" spans="1:16" ht="9.6">
       <c r="A31" s="19" t="s">
         <v>37</v>
       </c>
@@ -3125,7 +3272,7 @@
         <v>5036686</v>
       </c>
     </row>
-    <row r="32" spans="1:16" ht="9">
+    <row r="32" spans="1:16" ht="9.6">
       <c r="A32" s="19" t="s">
         <v>36</v>
       </c>
@@ -3175,7 +3322,7 @@
         <v>8453239</v>
       </c>
     </row>
-    <row r="33" spans="1:16" ht="9">
+    <row r="33" spans="1:16" ht="9.6">
       <c r="A33" s="43" t="s">
         <v>35</v>
       </c>
@@ -3225,7 +3372,7 @@
         <v>5690749</v>
       </c>
     </row>
-    <row r="34" spans="1:16" ht="9">
+    <row r="34" spans="1:16" ht="9.6">
       <c r="A34" s="19" t="s">
         <v>34</v>
       </c>
@@ -3275,7 +3422,7 @@
         <v>2058975</v>
       </c>
     </row>
-    <row r="35" spans="1:16" ht="9">
+    <row r="35" spans="1:16" ht="9.6">
       <c r="A35" s="19" t="s">
         <v>33</v>
       </c>
@@ -3325,7 +3472,7 @@
         <v>5587022</v>
       </c>
     </row>
-    <row r="36" spans="1:16" ht="9">
+    <row r="36" spans="1:16" ht="9.6">
       <c r="A36" s="19" t="s">
         <v>32</v>
       </c>
@@ -3375,7 +3522,7 @@
         <v>1952553</v>
       </c>
     </row>
-    <row r="37" spans="1:16" ht="9">
+    <row r="37" spans="1:16" ht="9.6">
       <c r="A37" s="19" t="s">
         <v>31</v>
       </c>
@@ -3425,7 +3572,7 @@
         <v>1935357</v>
       </c>
     </row>
-    <row r="38" spans="1:16" ht="9">
+    <row r="38" spans="1:16" ht="9.6">
       <c r="A38" s="52" t="s">
         <v>30</v>
       </c>
@@ -3475,7 +3622,7 @@
         <v>2549357</v>
       </c>
     </row>
-    <row r="39" spans="1:16" ht="9">
+    <row r="39" spans="1:16" ht="9.6">
       <c r="A39" s="19" t="s">
         <v>29</v>
       </c>
@@ -3525,7 +3672,7 @@
         <v>1357535</v>
       </c>
     </row>
-    <row r="40" spans="1:16" ht="9">
+    <row r="40" spans="1:16" ht="9.6">
       <c r="A40" s="19" t="s">
         <v>28</v>
       </c>
@@ -3575,7 +3722,7 @@
         <v>6006247</v>
       </c>
     </row>
-    <row r="41" spans="1:16" ht="9">
+    <row r="41" spans="1:16" ht="9.6">
       <c r="A41" s="43" t="s">
         <v>27</v>
       </c>
@@ -3625,7 +3772,7 @@
         <v>1783151</v>
       </c>
     </row>
-    <row r="42" spans="1:16" ht="9">
+    <row r="42" spans="1:16" ht="9.6">
       <c r="A42" s="19" t="s">
         <v>26</v>
       </c>
@@ -3675,7 +3822,7 @@
         <v>11324755</v>
       </c>
     </row>
-    <row r="43" spans="1:16" ht="9">
+    <row r="43" spans="1:16" ht="9.6">
       <c r="A43" s="19" t="s">
         <v>25</v>
       </c>
@@ -3725,7 +3872,7 @@
         <v>8739280</v>
       </c>
     </row>
-    <row r="44" spans="1:16" ht="9">
+    <row r="44" spans="1:16" ht="9.6">
       <c r="A44" s="19" t="s">
         <v>24</v>
       </c>
@@ -3775,7 +3922,7 @@
         <v>899083</v>
       </c>
     </row>
-    <row r="45" spans="1:16" ht="9">
+    <row r="45" spans="1:16" ht="9.6">
       <c r="A45" s="19" t="s">
         <v>23</v>
       </c>
@@ -3825,7 +3972,7 @@
         <v>10592317</v>
       </c>
     </row>
-    <row r="46" spans="1:16" ht="9">
+    <row r="46" spans="1:16" ht="9.6">
       <c r="A46" s="52" t="s">
         <v>22</v>
       </c>
@@ -3875,7 +4022,7 @@
         <v>3730247</v>
       </c>
     </row>
-    <row r="47" spans="1:16" ht="9">
+    <row r="47" spans="1:16" ht="9.6">
       <c r="A47" s="19" t="s">
         <v>21</v>
       </c>
@@ -3925,7 +4072,7 @@
         <v>4095442</v>
       </c>
     </row>
-    <row r="48" spans="1:16" ht="9">
+    <row r="48" spans="1:16" ht="9.6">
       <c r="A48" s="19" t="s">
         <v>20</v>
       </c>
@@ -3975,7 +4122,7 @@
         <v>10690187</v>
       </c>
     </row>
-    <row r="49" spans="1:16" ht="9">
+    <row r="49" spans="1:16" ht="9.6">
       <c r="A49" s="43" t="s">
         <v>19</v>
       </c>
@@ -4025,7 +4172,7 @@
         <v>866625</v>
       </c>
     </row>
-    <row r="50" spans="1:16" ht="9">
+    <row r="50" spans="1:16" ht="9.6">
       <c r="A50" s="19" t="s">
         <v>18</v>
       </c>
@@ -4075,7 +4222,7 @@
         <v>4561299</v>
       </c>
     </row>
-    <row r="51" spans="1:16" ht="9">
+    <row r="51" spans="1:16" ht="9.6">
       <c r="A51" s="19" t="s">
         <v>17</v>
       </c>
@@ -4125,7 +4272,7 @@
         <v>1294282</v>
       </c>
     </row>
-    <row r="52" spans="1:16" ht="9">
+    <row r="52" spans="1:16" ht="9.6">
       <c r="A52" s="19" t="s">
         <v>16</v>
       </c>
@@ -4175,7 +4322,7 @@
         <v>5855373</v>
       </c>
     </row>
-    <row r="53" spans="1:16" ht="9">
+    <row r="53" spans="1:16" ht="9.6">
       <c r="A53" s="19" t="s">
         <v>15</v>
       </c>
@@ -4225,7 +4372,7 @@
         <v>22419490</v>
       </c>
     </row>
-    <row r="54" spans="1:16" ht="9">
+    <row r="54" spans="1:16" ht="9.6">
       <c r="A54" s="52" t="s">
         <v>14</v>
       </c>
@@ -4275,7 +4422,7 @@
         <v>2479604</v>
       </c>
     </row>
-    <row r="55" spans="1:16" ht="9">
+    <row r="55" spans="1:16" ht="9.6">
       <c r="A55" s="19" t="s">
         <v>13</v>
       </c>
@@ -4325,7 +4472,7 @@
         <v>607890</v>
       </c>
     </row>
-    <row r="56" spans="1:16" ht="9">
+    <row r="56" spans="1:16" ht="9.6">
       <c r="A56" s="19" t="s">
         <v>12</v>
       </c>
@@ -4375,7 +4522,7 @@
         <v>7606452</v>
       </c>
     </row>
-    <row r="57" spans="1:16" ht="9">
+    <row r="57" spans="1:16" ht="9.6">
       <c r="A57" s="43" t="s">
         <v>11</v>
       </c>
@@ -4425,7 +4572,7 @@
         <v>7257401</v>
       </c>
     </row>
-    <row r="58" spans="1:16" ht="9">
+    <row r="58" spans="1:16" ht="9.6">
       <c r="A58" s="19" t="s">
         <v>10</v>
       </c>
@@ -4475,7 +4622,7 @@
         <v>1657362</v>
       </c>
     </row>
-    <row r="59" spans="1:16" ht="9">
+    <row r="59" spans="1:16" ht="9.6">
       <c r="A59" s="19" t="s">
         <v>9</v>
       </c>
@@ -4525,7 +4672,7 @@
         <v>5616271</v>
       </c>
     </row>
-    <row r="60" spans="1:16" ht="9">
+    <row r="60" spans="1:16" ht="9.6">
       <c r="A60" s="19" t="s">
         <v>8</v>
       </c>
@@ -4575,7 +4722,7 @@
         <v>861028</v>
       </c>
     </row>
-    <row r="61" spans="1:16" ht="9">
+    <row r="61" spans="1:16" ht="9.6">
       <c r="A61" s="11" t="s">
         <v>7</v>
       </c>
@@ -4625,7 +4772,7 @@
         <v>275913237</v>
       </c>
     </row>
-    <row r="62" spans="1:16" ht="9">
+    <row r="62" spans="1:16" ht="9.6">
       <c r="A62" s="5"/>
       <c r="B62" s="5"/>
       <c r="C62" s="5"/>
@@ -4715,15 +4862,15 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="99" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
         <v>77</v>
@@ -4746,41 +4893,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B2">
-        <f>'Table MV-1'!D10/'Table MV-1'!$D$61</f>
-        <v>1.9359587122498342E-2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <f>'Table MV-1'!G10/'Table MV-1'!$G$61</f>
-        <v>5.5878521842202787E-3</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <f>'Table MV-1'!M10/'Table MV-1'!$M$61</f>
-        <v>1.3796718114729099E-2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B3">
-        <f>'Table MV-1'!D11/'Table MV-1'!$D$61</f>
-        <v>1.6278452622477892E-3</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>'Table MV-1'!G11/'Table MV-1'!$G$61</f>
-        <v>8.5645956308639404E-3</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -4792,21 +4934,18 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <f>'Table MV-1'!M11/'Table MV-1'!$M$61</f>
-        <v>3.2157240392212427E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B4">
-        <f>'Table MV-1'!D12/'Table MV-1'!$D$61</f>
-        <v>2.2923014439488926E-2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>'Table MV-1'!G12/'Table MV-1'!$G$61</f>
-        <v>8.4314569052797456E-3</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -4818,21 +4957,18 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <f>'Table MV-1'!M12/'Table MV-1'!$M$61</f>
-        <v>1.4537940044235568E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="B5">
-        <f>'Table MV-1'!D13/'Table MV-1'!$D$61</f>
-        <v>8.298230946218824E-3</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>'Table MV-1'!G13/'Table MV-1'!$G$61</f>
-        <v>1.1966588141313841E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -4844,21 +4980,18 @@
         <v>0</v>
       </c>
       <c r="G5">
-        <f>'Table MV-1'!M13/'Table MV-1'!$M$61</f>
-        <v>2.0388346017237942E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B6">
-        <f>'Table MV-1'!D14/'Table MV-1'!$D$61</f>
-        <v>0.13507737172957132</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <f>'Table MV-1'!G14/'Table MV-1'!$G$61</f>
-        <v>0.10017993599405446</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -4870,21 +5003,18 @@
         <v>0</v>
       </c>
       <c r="G6">
-        <f>'Table MV-1'!M14/'Table MV-1'!$M$61</f>
-        <v>9.4309653776233349E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="B7">
-        <f>'Table MV-1'!D15/'Table MV-1'!$D$61</f>
-        <v>1.5589702031572649E-2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <f>'Table MV-1'!G15/'Table MV-1'!$G$61</f>
-        <v>1.3631815783695276E-2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -4896,21 +5026,18 @@
         <v>0</v>
       </c>
       <c r="G7">
-        <f>'Table MV-1'!M15/'Table MV-1'!$M$61</f>
-        <v>2.1503721119001361E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B8">
-        <f>'Table MV-1'!D16/'Table MV-1'!$D$61</f>
-        <v>1.1520117410612801E-2</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <f>'Table MV-1'!G16/'Table MV-1'!$G$61</f>
-        <v>1.169732997240849E-2</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -4922,21 +5049,18 @@
         <v>0</v>
       </c>
       <c r="G8">
-        <f>'Table MV-1'!M16/'Table MV-1'!$M$61</f>
-        <v>9.7199374650282049E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="B9">
-        <f>'Table MV-1'!D17/'Table MV-1'!$D$61</f>
-        <v>3.955997652548668E-3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <f>'Table MV-1'!G17/'Table MV-1'!$G$61</f>
-        <v>3.8341965823090428E-3</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -4948,21 +5072,18 @@
         <v>0</v>
       </c>
       <c r="G9">
-        <f>'Table MV-1'!M17/'Table MV-1'!$M$61</f>
-        <v>4.8306104364239793E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="B10">
-        <f>'Table MV-1'!D18/'Table MV-1'!$D$61</f>
-        <v>2.0002511050046939E-3</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <f>'Table MV-1'!G18/'Table MV-1'!$G$61</f>
-        <v>5.1000080479378894E-3</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -4974,21 +5095,18 @@
         <v>0</v>
       </c>
       <c r="G10">
-        <f>'Table MV-1'!M18/'Table MV-1'!$M$61</f>
-        <v>4.2830692087308811E-4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B11">
-        <f>'Table MV-1'!D19/'Table MV-1'!$D$61</f>
-        <v>7.4585348593669304E-2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <f>'Table MV-1'!G19/'Table MV-1'!$G$61</f>
-        <v>5.9786242795356839E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -5000,21 +5118,18 @@
         <v>0</v>
       </c>
       <c r="G11">
-        <f>'Table MV-1'!M19/'Table MV-1'!$M$61</f>
-        <v>7.4455640755318714E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B12">
-        <f>'Table MV-1'!D20/'Table MV-1'!$D$61</f>
-        <v>3.3246882826224872E-2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <f>'Table MV-1'!G20/'Table MV-1'!$G$61</f>
-        <v>3.6664815309761158E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -5026,21 +5141,18 @@
         <v>0</v>
       </c>
       <c r="G12">
-        <f>'Table MV-1'!M20/'Table MV-1'!$M$61</f>
-        <v>2.4934379105058271E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="B13">
-        <f>'Table MV-1'!D21/'Table MV-1'!$D$61</f>
-        <v>4.5177880312321358E-3</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <f>'Table MV-1'!G21/'Table MV-1'!$G$61</f>
-        <v>2.8664568903761568E-3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -5052,21 +5164,18 @@
         <v>0</v>
       </c>
       <c r="G13">
-        <f>'Table MV-1'!M21/'Table MV-1'!$M$61</f>
-        <v>4.4403672368620124E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="B14">
-        <f>'Table MV-1'!D22/'Table MV-1'!$D$61</f>
-        <v>5.5962364686266176E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <f>'Table MV-1'!G22/'Table MV-1'!$G$61</f>
-        <v>3.782530808201743E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -5078,21 +5187,18 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <f>'Table MV-1'!M22/'Table MV-1'!$M$61</f>
-        <v>7.1114318443253836E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="B15">
-        <f>'Table MV-1'!D23/'Table MV-1'!$D$61</f>
-        <v>3.9583802966272987E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <f>'Table MV-1'!G23/'Table MV-1'!$G$61</f>
-        <v>3.2598122743969261E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -5104,21 +5210,18 @@
         <v>0</v>
       </c>
       <c r="G15">
-        <f>'Table MV-1'!M23/'Table MV-1'!$M$61</f>
-        <v>3.3659616673110682E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="B16">
-        <f>'Table MV-1'!D24/'Table MV-1'!$D$61</f>
-        <v>2.0200142102604929E-2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <f>'Table MV-1'!G24/'Table MV-1'!$G$61</f>
-        <v>2.0735859723449008E-2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -5130,21 +5233,18 @@
         <v>0</v>
       </c>
       <c r="G16">
-        <f>'Table MV-1'!M24/'Table MV-1'!$M$61</f>
-        <v>2.519458126304313E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="B17">
-        <f>'Table MV-1'!D25/'Table MV-1'!$D$61</f>
-        <v>1.1069079557484499E-2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <f>'Table MV-1'!G25/'Table MV-1'!$G$61</f>
-        <v>9.1140412670434948E-3</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -5156,21 +5256,18 @@
         <v>0</v>
       </c>
       <c r="G17">
-        <f>'Table MV-1'!M25/'Table MV-1'!$M$61</f>
-        <v>2.3030832815010314E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B18">
-        <f>'Table MV-1'!D26/'Table MV-1'!$D$61</f>
-        <v>8.4565602609209273E-3</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <f>'Table MV-1'!G26/'Table MV-1'!$G$61</f>
-        <v>6.5585725938901249E-3</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -5182,21 +5279,18 @@
         <v>0</v>
       </c>
       <c r="G18">
-        <f>'Table MV-1'!M26/'Table MV-1'!$M$61</f>
-        <v>1.0883942873198577E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="B19">
-        <f>'Table MV-1'!D27/'Table MV-1'!$D$61</f>
-        <v>1.5641720716067772E-2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <f>'Table MV-1'!G27/'Table MV-1'!$G$61</f>
-        <v>1.0917375497904058E-2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -5208,21 +5302,18 @@
         <v>0</v>
       </c>
       <c r="G19">
-        <f>'Table MV-1'!M27/'Table MV-1'!$M$61</f>
-        <v>1.166599024512076E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B20">
-        <f>'Table MV-1'!D28/'Table MV-1'!$D$61</f>
-        <v>1.2514264951923855E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <f>'Table MV-1'!G28/'Table MV-1'!$G$61</f>
-        <v>2.9889643893651965E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -5234,21 +5325,18 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <f>'Table MV-1'!M28/'Table MV-1'!$M$61</f>
-        <v>1.2186394561090472E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="B21">
-        <f>'Table MV-1'!D29/'Table MV-1'!$D$61</f>
-        <v>3.3868643547885439E-3</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <f>'Table MV-1'!G29/'Table MV-1'!$G$61</f>
-        <v>4.5932860326547567E-3</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -5260,21 +5348,18 @@
         <v>0</v>
       </c>
       <c r="G21">
-        <f>'Table MV-1'!M29/'Table MV-1'!$M$61</f>
-        <v>4.6036690065248661E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="B22">
-        <f>'Table MV-1'!D30/'Table MV-1'!$D$61</f>
-        <v>1.7344821387298082E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <f>'Table MV-1'!G30/'Table MV-1'!$G$61</f>
-        <v>2.2395125930356523E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -5286,21 +5371,18 @@
         <v>0</v>
       </c>
       <c r="G22">
-        <f>'Table MV-1'!M30/'Table MV-1'!$M$61</f>
-        <v>1.3514422187907504E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="B23">
-        <f>'Table MV-1'!D31/'Table MV-1'!$D$61</f>
-        <v>1.9055188885179382E-2</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <f>'Table MV-1'!G31/'Table MV-1'!$G$61</f>
-        <v>1.3663610106222844E-2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -5312,21 +5394,18 @@
         <v>0</v>
       </c>
       <c r="G23">
-        <f>'Table MV-1'!M31/'Table MV-1'!$M$61</f>
-        <v>1.6585095831722331E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="B24">
-        <f>'Table MV-1'!D32/'Table MV-1'!$D$61</f>
-        <v>2.5602285816466973E-2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <f>'Table MV-1'!G32/'Table MV-1'!$G$61</f>
-        <v>8.8845260012976063E-3</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -5338,21 +5417,18 @@
         <v>0</v>
       </c>
       <c r="G24">
-        <f>'Table MV-1'!M32/'Table MV-1'!$M$61</f>
-        <v>2.8515490853900149E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="B25">
-        <f>'Table MV-1'!D33/'Table MV-1'!$D$61</f>
-        <v>1.7517332427833467E-2</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <f>'Table MV-1'!G33/'Table MV-1'!$G$61</f>
-        <v>1.9068644935909602E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -5364,21 +5440,18 @@
         <v>0</v>
       </c>
       <c r="G25">
-        <f>'Table MV-1'!M33/'Table MV-1'!$M$61</f>
-        <v>2.9294896579548375E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="B26">
-        <f>'Table MV-1'!D34/'Table MV-1'!$D$61</f>
-        <v>7.4991463380995726E-3</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <f>'Table MV-1'!G34/'Table MV-1'!$G$61</f>
-        <v>7.3385270683945557E-3</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -5390,21 +5463,18 @@
         <v>0</v>
       </c>
       <c r="G26">
-        <f>'Table MV-1'!M34/'Table MV-1'!$M$61</f>
-        <v>3.6710477969870824E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B27">
-        <f>'Table MV-1'!D35/'Table MV-1'!$D$61</f>
-        <v>1.8941078781341755E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <f>'Table MV-1'!G35/'Table MV-1'!$G$61</f>
-        <v>3.3533074540795592E-2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -5416,21 +5486,18 @@
         <v>0</v>
       </c>
       <c r="G27">
-        <f>'Table MV-1'!M35/'Table MV-1'!$M$61</f>
-        <v>1.5214201490368798E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B28">
-        <f>'Table MV-1'!D36/'Table MV-1'!$D$61</f>
-        <v>4.3665733583296952E-3</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <f>'Table MV-1'!G36/'Table MV-1'!$G$61</f>
-        <v>5.1616095478350553E-3</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -5442,21 +5509,18 @@
         <v>0</v>
       </c>
       <c r="G28">
-        <f>'Table MV-1'!M36/'Table MV-1'!$M$61</f>
-        <v>4.2647577970591273E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="B29">
-        <f>'Table MV-1'!D37/'Table MV-1'!$D$61</f>
-        <v>5.9438361806167864E-3</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <f>'Table MV-1'!G37/'Table MV-1'!$G$61</f>
-        <v>1.7177876318098223E-2</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -5468,21 +5532,18 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <f>'Table MV-1'!M37/'Table MV-1'!$M$61</f>
-        <v>6.0485294435492195E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B30">
-        <f>'Table MV-1'!D38/'Table MV-1'!$D$61</f>
-        <v>9.7731494559867137E-3</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <f>'Table MV-1'!G38/'Table MV-1'!$G$61</f>
-        <v>3.1883744059677944E-3</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -5494,21 +5555,18 @@
         <v>0</v>
       </c>
       <c r="G30">
-        <f>'Table MV-1'!M38/'Table MV-1'!$M$61</f>
-        <v>8.327909953483011E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="B31">
-        <f>'Table MV-1'!D39/'Table MV-1'!$D$61</f>
-        <v>4.3831615071246288E-3</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <f>'Table MV-1'!G39/'Table MV-1'!$G$61</f>
-        <v>3.0602035432785312E-3</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -5520,21 +5578,18 @@
         <v>0</v>
       </c>
       <c r="G31">
-        <f>'Table MV-1'!M39/'Table MV-1'!$M$61</f>
-        <v>9.4484482729637106E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="B32">
-        <f>'Table MV-1'!D40/'Table MV-1'!$D$61</f>
-        <v>2.4170045645943845E-2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <f>'Table MV-1'!G40/'Table MV-1'!$G$61</f>
-        <v>2.5791157005332504E-2</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -5546,21 +5601,18 @@
         <v>0</v>
       </c>
       <c r="G32">
-        <f>'Table MV-1'!M40/'Table MV-1'!$M$61</f>
-        <v>1.4574562867579076E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="B33">
-        <f>'Table MV-1'!D41/'Table MV-1'!$D$61</f>
-        <v>5.9347811819626707E-3</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <f>'Table MV-1'!G41/'Table MV-1'!$G$61</f>
-        <v>9.7280691208571756E-3</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -5572,21 +5624,18 @@
         <v>0</v>
       </c>
       <c r="G33">
-        <f>'Table MV-1'!M41/'Table MV-1'!$M$61</f>
-        <v>6.5976316440405662E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B34">
-        <f>'Table MV-1'!D42/'Table MV-1'!$D$61</f>
-        <v>4.0260007818496736E-2</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <f>'Table MV-1'!G42/'Table MV-1'!$G$61</f>
-        <v>8.1156995396778245E-2</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -5598,21 +5647,18 @@
         <v>0</v>
       </c>
       <c r="G34">
-        <f>'Table MV-1'!M42/'Table MV-1'!$M$61</f>
-        <v>4.6183181358622691E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="B35">
-        <f>'Table MV-1'!D43/'Table MV-1'!$D$61</f>
-        <v>3.232472823114596E-2</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <f>'Table MV-1'!G43/'Table MV-1'!$G$61</f>
-        <v>3.311776120277922E-2</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -5624,21 +5670,18 @@
         <v>0</v>
       </c>
       <c r="G35">
-        <f>'Table MV-1'!M43/'Table MV-1'!$M$61</f>
-        <v>2.2775793874742739E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B36">
-        <f>'Table MV-1'!D44/'Table MV-1'!$D$61</f>
-        <v>2.0512044955405084E-3</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <f>'Table MV-1'!G44/'Table MV-1'!$G$61</f>
-        <v>3.6394563568276817E-3</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -5650,21 +5693,18 @@
         <v>0</v>
       </c>
       <c r="G36">
-        <f>'Table MV-1'!M44/'Table MV-1'!$M$61</f>
-        <v>4.3507914132087117E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="B37">
-        <f>'Table MV-1'!D45/'Table MV-1'!$D$61</f>
-        <v>4.0403584714173067E-2</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <f>'Table MV-1'!G45/'Table MV-1'!$G$61</f>
-        <v>4.1215377721519487E-2</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -5676,21 +5716,18 @@
         <v>0</v>
       </c>
       <c r="G37">
-        <f>'Table MV-1'!M45/'Table MV-1'!$M$61</f>
-        <v>4.5702521811592983E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="B38">
-        <f>'Table MV-1'!D46/'Table MV-1'!$D$61</f>
-        <v>1.1640695370631938E-2</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <f>'Table MV-1'!G46/'Table MV-1'!$G$61</f>
-        <v>2.8227396969007492E-3</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -5702,21 +5739,18 @@
         <v>0</v>
       </c>
       <c r="G38">
-        <f>'Table MV-1'!M46/'Table MV-1'!$M$61</f>
-        <v>1.6077419447799869E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="B39">
-        <f>'Table MV-1'!D47/'Table MV-1'!$D$61</f>
-        <v>1.3704702416790554E-2</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <f>'Table MV-1'!G47/'Table MV-1'!$G$61</f>
-        <v>1.772632838169879E-2</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -5728,21 +5762,18 @@
         <v>0</v>
       </c>
       <c r="G39">
-        <f>'Table MV-1'!M47/'Table MV-1'!$M$61</f>
-        <v>1.4843290338538977E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B40">
-        <f>'Table MV-1'!D48/'Table MV-1'!$D$61</f>
-        <v>3.846201038090917E-2</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <f>'Table MV-1'!G48/'Table MV-1'!$G$61</f>
-        <v>5.4911775722848888E-2</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -5754,21 +5785,18 @@
         <v>0</v>
       </c>
       <c r="G40">
-        <f>'Table MV-1'!M48/'Table MV-1'!$M$61</f>
-        <v>4.3286135919905287E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="B41">
-        <f>'Table MV-1'!D49/'Table MV-1'!$D$61</f>
-        <v>3.6311971335983252E-3</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <f>'Table MV-1'!G49/'Table MV-1'!$G$61</f>
-        <v>2.3031012380907907E-3</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -5780,21 +5808,18 @@
         <v>0</v>
       </c>
       <c r="G41">
-        <f>'Table MV-1'!M49/'Table MV-1'!$M$61</f>
-        <v>2.8346065267874938E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="B42">
-        <f>'Table MV-1'!D50/'Table MV-1'!$D$61</f>
-        <v>1.6810224539236585E-2</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <f>'Table MV-1'!G50/'Table MV-1'!$G$61</f>
-        <v>1.6360166085592303E-2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -5806,21 +5831,18 @@
         <v>0</v>
       </c>
       <c r="G42">
-        <f>'Table MV-1'!M50/'Table MV-1'!$M$61</f>
-        <v>1.3750249155273566E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="B43">
-        <f>'Table MV-1'!D51/'Table MV-1'!$D$61</f>
-        <v>3.0912643041870807E-3</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <f>'Table MV-1'!G51/'Table MV-1'!$G$61</f>
-        <v>2.6518452133150647E-3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -5832,21 +5854,18 @@
         <v>0</v>
       </c>
       <c r="G43">
-        <f>'Table MV-1'!M51/'Table MV-1'!$M$61</f>
-        <v>1.5581990696602122E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="B44">
-        <f>'Table MV-1'!D52/'Table MV-1'!$D$61</f>
-        <v>2.0122946336767956E-2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <f>'Table MV-1'!G52/'Table MV-1'!$G$61</f>
-        <v>2.9370005434842007E-2</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -5858,21 +5877,18 @@
         <v>0</v>
       </c>
       <c r="G44">
-        <f>'Table MV-1'!M52/'Table MV-1'!$M$61</f>
-        <v>2.12856652265692E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="B45">
-        <f>'Table MV-1'!D53/'Table MV-1'!$D$61</f>
-        <v>7.6929994017233036E-2</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>'Table MV-1'!G53/'Table MV-1'!$G$61</f>
-        <v>7.0475096600093989E-2</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -5884,21 +5900,18 @@
         <v>0</v>
       </c>
       <c r="G45">
-        <f>'Table MV-1'!M53/'Table MV-1'!$M$61</f>
-        <v>3.9420566897290392E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="B46">
-        <f>'Table MV-1'!D54/'Table MV-1'!$D$61</f>
-        <v>8.5862978466794693E-3</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <f>'Table MV-1'!G54/'Table MV-1'!$G$61</f>
-        <v>6.3797295296725487E-3</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -5910,21 +5923,18 @@
         <v>0</v>
       </c>
       <c r="G46">
-        <f>'Table MV-1'!M54/'Table MV-1'!$M$61</f>
-        <v>1.4880153311543754E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="B47">
-        <f>'Table MV-1'!D55/'Table MV-1'!$D$61</f>
-        <v>1.8396009713198137E-3</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <f>'Table MV-1'!G55/'Table MV-1'!$G$61</f>
-        <v>1.0720648127264725E-3</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -5936,21 +5946,18 @@
         <v>0</v>
       </c>
       <c r="G47">
-        <f>'Table MV-1'!M55/'Table MV-1'!$M$61</f>
-        <v>3.4752057482222922E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="B48">
-        <f>'Table MV-1'!D56/'Table MV-1'!$D$61</f>
-        <v>2.9079234091689471E-2</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <f>'Table MV-1'!G56/'Table MV-1'!$G$61</f>
-        <v>3.5235064368599529E-2</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -5962,21 +5969,18 @@
         <v>0</v>
       </c>
       <c r="G48">
-        <f>'Table MV-1'!M56/'Table MV-1'!$M$61</f>
-        <v>2.2146721837048848E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B49">
-        <f>'Table MV-1'!D57/'Table MV-1'!$D$61</f>
-        <v>2.6635868257378827E-2</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <f>'Table MV-1'!G57/'Table MV-1'!$G$61</f>
-        <v>2.4016636379262549E-2</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -5988,21 +5992,18 @@
         <v>0</v>
       </c>
       <c r="G49">
-        <f>'Table MV-1'!M57/'Table MV-1'!$M$61</f>
-        <v>2.6590331094337991E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="B50">
-        <f>'Table MV-1'!D58/'Table MV-1'!$D$61</f>
-        <v>4.8381751894939189E-3</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <f>'Table MV-1'!G58/'Table MV-1'!$G$61</f>
-        <v>3.1347214867025212E-3</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -6014,21 +6015,18 @@
         <v>0</v>
       </c>
       <c r="G50">
-        <f>'Table MV-1'!M58/'Table MV-1'!$M$61</f>
-        <v>5.2267373026870347E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="B51">
-        <f>'Table MV-1'!D59/'Table MV-1'!$D$61</f>
-        <v>1.8086189890550556E-2</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <f>'Table MV-1'!G59/'Table MV-1'!$G$61</f>
-        <v>1.4844967902637837E-2</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -6040,21 +6038,18 @@
         <v>0</v>
       </c>
       <c r="G51">
-        <f>'Table MV-1'!M59/'Table MV-1'!$M$61</f>
-        <v>3.3177876452605261E-2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="B52">
-        <f>'Table MV-1'!D60/'Table MV-1'!$D$61</f>
-        <v>1.8198644984129973E-3</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <f>'Table MV-1'!G60/'Table MV-1'!$G$61</f>
-        <v>4.0746411464237849E-3</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -6066,13 +6061,12 @@
         <v>0</v>
       </c>
       <c r="G52">
-        <f>'Table MV-1'!M60/'Table MV-1'!$M$61</f>
-        <v>3.420691775114251E-3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -6095,7 +6089,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -6118,7 +6112,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -6141,7 +6135,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -6164,7 +6158,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -6187,7 +6181,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -6210,7 +6204,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -6233,7 +6227,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -6256,7 +6250,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -6289,15 +6283,15 @@
     <tabColor theme="4" tint="-0.249977111117893"/>
   </sheetPr>
   <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="20" customWidth="1"/>
-    <col min="2" max="7" width="13.7109375" customWidth="1"/>
+    <col min="2" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="99" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B1" t="s">
         <v>77</v>
@@ -6320,40 +6314,36 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="B2">
-        <f>C2</f>
-        <v>1.9600927701391289E-2</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <f>'Table MV-1'!J10/'Table MV-1'!$J$61</f>
-        <v>1.9600927701391289E-2</v>
+        <v>1</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>107</v>
       </c>
       <c r="B3">
-        <f t="shared" ref="B3:B52" si="0">C3</f>
-        <v>3.6314972397001131E-3</v>
+        <v>0</v>
       </c>
       <c r="C3">
-        <f>'Table MV-1'!J11/'Table MV-1'!$J$61</f>
-        <v>3.6314972397001131E-3</v>
+        <v>0</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -6370,15 +6360,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" t="s">
-        <v>56</v>
+        <v>108</v>
       </c>
       <c r="B4">
-        <f t="shared" si="0"/>
-        <v>2.1767409304149131E-2</v>
+        <v>0</v>
       </c>
       <c r="C4">
-        <f>'Table MV-1'!J12/'Table MV-1'!$J$61</f>
-        <v>2.1767409304149131E-2</v>
+        <v>0</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -6395,15 +6383,13 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" t="s">
-        <v>55</v>
+        <v>109</v>
       </c>
       <c r="B5">
-        <f t="shared" si="0"/>
-        <v>1.1515440266444459E-2</v>
+        <v>0</v>
       </c>
       <c r="C5">
-        <f>'Table MV-1'!J13/'Table MV-1'!$J$61</f>
-        <v>1.1515440266444459E-2</v>
+        <v>0</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -6420,15 +6406,13 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>54</v>
+        <v>110</v>
       </c>
       <c r="B6">
-        <f t="shared" si="0"/>
-        <v>9.483573703336938E-2</v>
+        <v>0</v>
       </c>
       <c r="C6">
-        <f>'Table MV-1'!J14/'Table MV-1'!$J$61</f>
-        <v>9.483573703336938E-2</v>
+        <v>0</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -6445,15 +6429,13 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>111</v>
       </c>
       <c r="B7">
-        <f t="shared" si="0"/>
-        <v>2.17963420575671E-2</v>
+        <v>0</v>
       </c>
       <c r="C7">
-        <f>'Table MV-1'!J15/'Table MV-1'!$J$61</f>
-        <v>2.17963420575671E-2</v>
+        <v>0</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -6470,15 +6452,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>112</v>
       </c>
       <c r="B8">
-        <f t="shared" si="0"/>
-        <v>9.6855101995915252E-3</v>
+        <v>0</v>
       </c>
       <c r="C8">
-        <f>'Table MV-1'!J16/'Table MV-1'!$J$61</f>
-        <v>9.6855101995915252E-3</v>
+        <v>0</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -6495,15 +6475,13 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>113</v>
       </c>
       <c r="B9">
-        <f t="shared" si="0"/>
-        <v>3.607073808587494E-3</v>
+        <v>0</v>
       </c>
       <c r="C9">
-        <f>'Table MV-1'!J17/'Table MV-1'!$J$61</f>
-        <v>3.607073808587494E-3</v>
+        <v>0</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -6520,15 +6498,13 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10" t="s">
-        <v>84</v>
+        <v>114</v>
       </c>
       <c r="B10">
-        <f t="shared" si="0"/>
-        <v>8.5193982126037439E-4</v>
+        <v>0</v>
       </c>
       <c r="C10">
-        <f>'Table MV-1'!J18/'Table MV-1'!$J$61</f>
-        <v>8.5193982126037439E-4</v>
+        <v>0</v>
       </c>
       <c r="D10">
         <v>0</v>
@@ -6545,15 +6521,13 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11" t="s">
-        <v>49</v>
+        <v>115</v>
       </c>
       <c r="B11">
-        <f t="shared" si="0"/>
-        <v>6.1586335732623156E-2</v>
+        <v>0</v>
       </c>
       <c r="C11">
-        <f>'Table MV-1'!J19/'Table MV-1'!$J$61</f>
-        <v>6.1586335732623156E-2</v>
+        <v>0</v>
       </c>
       <c r="D11">
         <v>0</v>
@@ -6570,15 +6544,13 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="B12">
-        <f t="shared" si="0"/>
-        <v>3.1525712849526988E-2</v>
+        <v>0</v>
       </c>
       <c r="C12">
-        <f>'Table MV-1'!J20/'Table MV-1'!$J$61</f>
-        <v>3.1525712849526988E-2</v>
+        <v>0</v>
       </c>
       <c r="D12">
         <v>0</v>
@@ -6595,15 +6567,13 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13" t="s">
-        <v>47</v>
+        <v>117</v>
       </c>
       <c r="B13">
-        <f t="shared" si="0"/>
-        <v>4.5222742187277015E-3</v>
+        <v>0</v>
       </c>
       <c r="C13">
-        <f>'Table MV-1'!J21/'Table MV-1'!$J$61</f>
-        <v>4.5222742187277015E-3</v>
+        <v>0</v>
       </c>
       <c r="D13">
         <v>0</v>
@@ -6620,15 +6590,13 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14" t="s">
-        <v>46</v>
+        <v>118</v>
       </c>
       <c r="B14">
-        <f t="shared" si="0"/>
-        <v>7.8435139790973586E-3</v>
+        <v>0</v>
       </c>
       <c r="C14">
-        <f>'Table MV-1'!J22/'Table MV-1'!$J$61</f>
-        <v>7.8435139790973586E-3</v>
+        <v>0</v>
       </c>
       <c r="D14">
         <v>0</v>
@@ -6645,15 +6613,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15" t="s">
-        <v>45</v>
+        <v>119</v>
       </c>
       <c r="B15">
-        <f t="shared" si="0"/>
-        <v>3.7864302450454933E-2</v>
+        <v>0</v>
       </c>
       <c r="C15">
-        <f>'Table MV-1'!J23/'Table MV-1'!$J$61</f>
-        <v>3.7864302450454933E-2</v>
+        <v>0</v>
       </c>
       <c r="D15">
         <v>0</v>
@@ -6670,15 +6636,13 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16" t="s">
-        <v>44</v>
+        <v>120</v>
       </c>
       <c r="B16">
-        <f t="shared" si="0"/>
-        <v>2.3819250059067168E-2</v>
+        <v>0</v>
       </c>
       <c r="C16">
-        <f>'Table MV-1'!J24/'Table MV-1'!$J$61</f>
-        <v>2.3819250059067168E-2</v>
+        <v>0</v>
       </c>
       <c r="D16">
         <v>0</v>
@@ -6695,15 +6659,13 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17" t="s">
-        <v>43</v>
+        <v>121</v>
       </c>
       <c r="B17">
-        <f t="shared" si="0"/>
-        <v>1.5005240724472678E-2</v>
+        <v>0</v>
       </c>
       <c r="C17">
-        <f>'Table MV-1'!J25/'Table MV-1'!$J$61</f>
-        <v>1.5005240724472678E-2</v>
+        <v>0</v>
       </c>
       <c r="D17">
         <v>0</v>
@@ -6720,15 +6682,13 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>42</v>
+        <v>122</v>
       </c>
       <c r="B18">
-        <f t="shared" si="0"/>
-        <v>1.0017236512864749E-2</v>
+        <v>0</v>
       </c>
       <c r="C18">
-        <f>'Table MV-1'!J26/'Table MV-1'!$J$61</f>
-        <v>1.0017236512864749E-2</v>
+        <v>0</v>
       </c>
       <c r="D18">
         <v>0</v>
@@ -6745,15 +6705,13 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19" t="s">
-        <v>41</v>
+        <v>123</v>
       </c>
       <c r="B19">
-        <f t="shared" si="0"/>
-        <v>1.6767766333459132E-2</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <f>'Table MV-1'!J27/'Table MV-1'!$J$61</f>
-        <v>1.6767766333459132E-2</v>
+        <v>0</v>
       </c>
       <c r="D19">
         <v>0</v>
@@ -6770,15 +6728,13 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20" t="s">
-        <v>40</v>
+        <v>124</v>
       </c>
       <c r="B20">
-        <f t="shared" si="0"/>
-        <v>1.4952243799136747E-2</v>
+        <v>0</v>
       </c>
       <c r="C20">
-        <f>'Table MV-1'!J28/'Table MV-1'!$J$61</f>
-        <v>1.4952243799136747E-2</v>
+        <v>0</v>
       </c>
       <c r="D20">
         <v>0</v>
@@ -6795,15 +6751,13 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>39</v>
+        <v>125</v>
       </c>
       <c r="B21">
-        <f t="shared" si="0"/>
-        <v>4.472553985012004E-3</v>
+        <v>0</v>
       </c>
       <c r="C21">
-        <f>'Table MV-1'!J29/'Table MV-1'!$J$61</f>
-        <v>4.472553985012004E-3</v>
+        <v>0</v>
       </c>
       <c r="D21">
         <v>0</v>
@@ -6820,15 +6774,13 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>38</v>
+        <v>126</v>
       </c>
       <c r="B22">
-        <f t="shared" si="0"/>
-        <v>1.3953713838208291E-2</v>
+        <v>0</v>
       </c>
       <c r="C22">
-        <f>'Table MV-1'!J30/'Table MV-1'!$J$61</f>
-        <v>1.3953713838208291E-2</v>
+        <v>0</v>
       </c>
       <c r="D22">
         <v>0</v>
@@ -6845,15 +6797,13 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23" t="s">
-        <v>83</v>
+        <v>127</v>
       </c>
       <c r="B23">
-        <f t="shared" si="0"/>
-        <v>1.7847984402303698E-2</v>
+        <v>0</v>
       </c>
       <c r="C23">
-        <f>'Table MV-1'!J31/'Table MV-1'!$J$61</f>
-        <v>1.7847984402303698E-2</v>
+        <v>0</v>
       </c>
       <c r="D23">
         <v>0</v>
@@ -6870,15 +6820,13 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>36</v>
+        <v>128</v>
       </c>
       <c r="B24">
-        <f t="shared" si="0"/>
-        <v>3.4161287854521931E-2</v>
+        <v>0</v>
       </c>
       <c r="C24">
-        <f>'Table MV-1'!J32/'Table MV-1'!$J$61</f>
-        <v>3.4161287854521931E-2</v>
+        <v>0</v>
       </c>
       <c r="D24">
         <v>0</v>
@@ -6895,15 +6843,13 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25" t="s">
-        <v>35</v>
+        <v>129</v>
       </c>
       <c r="B25">
-        <f t="shared" si="0"/>
-        <v>2.221147844524117E-2</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <f>'Table MV-1'!J33/'Table MV-1'!$J$61</f>
-        <v>2.221147844524117E-2</v>
+        <v>0</v>
       </c>
       <c r="D25">
         <v>0</v>
@@ -6920,15 +6866,13 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="B26">
-        <f t="shared" si="0"/>
-        <v>7.63482155174601E-3</v>
+        <v>0</v>
       </c>
       <c r="C26">
-        <f>'Table MV-1'!J34/'Table MV-1'!$J$61</f>
-        <v>7.63482155174601E-3</v>
+        <v>0</v>
       </c>
       <c r="D26">
         <v>0</v>
@@ -6945,15 +6889,13 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>33</v>
+        <v>131</v>
       </c>
       <c r="B27">
-        <f t="shared" si="0"/>
-        <v>2.1277992980917738E-2</v>
+        <v>0</v>
       </c>
       <c r="C27">
-        <f>'Table MV-1'!J35/'Table MV-1'!$J$61</f>
-        <v>2.1277992980917738E-2</v>
+        <v>0</v>
       </c>
       <c r="D27">
         <v>0</v>
@@ -6970,15 +6912,13 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>32</v>
+        <v>132</v>
       </c>
       <c r="B28">
-        <f t="shared" si="0"/>
-        <v>7.0185743445526595E-3</v>
+        <v>0</v>
       </c>
       <c r="C28">
-        <f>'Table MV-1'!J36/'Table MV-1'!$J$61</f>
-        <v>7.0185743445526595E-3</v>
+        <v>0</v>
       </c>
       <c r="D28">
         <v>0</v>
@@ -6995,15 +6935,13 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29" t="s">
-        <v>31</v>
+        <v>133</v>
       </c>
       <c r="B29">
-        <f t="shared" si="0"/>
-        <v>7.6979830346411097E-3</v>
+        <v>0</v>
       </c>
       <c r="C29">
-        <f>'Table MV-1'!J37/'Table MV-1'!$J$61</f>
-        <v>7.6979830346411097E-3</v>
+        <v>0</v>
       </c>
       <c r="D29">
         <v>0</v>
@@ -7020,15 +6958,13 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>134</v>
       </c>
       <c r="B30">
-        <f t="shared" si="0"/>
-        <v>8.9770758442244206E-3</v>
+        <v>0</v>
       </c>
       <c r="C30">
-        <f>'Table MV-1'!J38/'Table MV-1'!$J$61</f>
-        <v>8.9770758442244206E-3</v>
+        <v>0</v>
       </c>
       <c r="D30">
         <v>0</v>
@@ -7045,15 +6981,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>29</v>
+        <v>135</v>
       </c>
       <c r="B31">
-        <f t="shared" si="0"/>
-        <v>5.0478518381385203E-3</v>
+        <v>0</v>
       </c>
       <c r="C31">
-        <f>'Table MV-1'!J39/'Table MV-1'!$J$61</f>
-        <v>5.0478518381385203E-3</v>
+        <v>0</v>
       </c>
       <c r="D31">
         <v>0</v>
@@ -7070,15 +7004,13 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32" t="s">
-        <v>28</v>
+        <v>136</v>
       </c>
       <c r="B32">
-        <f t="shared" si="0"/>
-        <v>2.0550771847319699E-2</v>
+        <v>0</v>
       </c>
       <c r="C32">
-        <f>'Table MV-1'!J40/'Table MV-1'!$J$61</f>
-        <v>2.0550771847319699E-2</v>
+        <v>0</v>
       </c>
       <c r="D32">
         <v>0</v>
@@ -7095,15 +7027,13 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>137</v>
       </c>
       <c r="B33">
-        <f t="shared" si="0"/>
-        <v>6.7792148090505171E-3</v>
+        <v>0</v>
       </c>
       <c r="C33">
-        <f>'Table MV-1'!J41/'Table MV-1'!$J$61</f>
-        <v>6.7792148090505171E-3</v>
+        <v>0</v>
       </c>
       <c r="D33">
         <v>0</v>
@@ -7120,15 +7050,13 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34" t="s">
-        <v>26</v>
+        <v>138</v>
       </c>
       <c r="B34">
-        <f t="shared" si="0"/>
-        <v>4.1040438660927506E-2</v>
+        <v>0</v>
       </c>
       <c r="C34">
-        <f>'Table MV-1'!J42/'Table MV-1'!$J$61</f>
-        <v>4.1040438660927506E-2</v>
+        <v>0</v>
       </c>
       <c r="D34">
         <v>0</v>
@@ -7145,15 +7073,13 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>25</v>
+        <v>139</v>
       </c>
       <c r="B35">
-        <f t="shared" si="0"/>
-        <v>3.1700275653385936E-2</v>
+        <v>0</v>
       </c>
       <c r="C35">
-        <f>'Table MV-1'!J43/'Table MV-1'!$J$61</f>
-        <v>3.1700275653385936E-2</v>
+        <v>0</v>
       </c>
       <c r="D35">
         <v>0</v>
@@ -7170,15 +7096,13 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="B36">
-        <f t="shared" si="0"/>
-        <v>3.986117035446643E-3</v>
+        <v>0</v>
       </c>
       <c r="C36">
-        <f>'Table MV-1'!J44/'Table MV-1'!$J$61</f>
-        <v>3.986117035446643E-3</v>
+        <v>0</v>
       </c>
       <c r="D36">
         <v>0</v>
@@ -7195,15 +7119,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>23</v>
+        <v>141</v>
       </c>
       <c r="B37">
-        <f t="shared" si="0"/>
-        <v>3.6683925395789657E-2</v>
+        <v>0</v>
       </c>
       <c r="C37">
-        <f>'Table MV-1'!J45/'Table MV-1'!$J$61</f>
-        <v>3.6683925395789657E-2</v>
+        <v>0</v>
       </c>
       <c r="D37">
         <v>0</v>
@@ -7220,15 +7142,13 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38" t="s">
-        <v>22</v>
+        <v>142</v>
       </c>
       <c r="B38">
-        <f t="shared" si="0"/>
-        <v>1.4677986568760525E-2</v>
+        <v>0</v>
       </c>
       <c r="C38">
-        <f>'Table MV-1'!J46/'Table MV-1'!$J$61</f>
-        <v>1.4677986568760525E-2</v>
+        <v>0</v>
       </c>
       <c r="D38">
         <v>0</v>
@@ -7245,15 +7165,13 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>21</v>
+        <v>143</v>
       </c>
       <c r="B39">
-        <f t="shared" si="0"/>
-        <v>1.5566676127984676E-2</v>
+        <v>0</v>
       </c>
       <c r="C39">
-        <f>'Table MV-1'!J47/'Table MV-1'!$J$61</f>
-        <v>1.5566676127984676E-2</v>
+        <v>0</v>
       </c>
       <c r="D39">
         <v>0</v>
@@ -7270,15 +7188,13 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40" t="s">
-        <v>20</v>
+        <v>144</v>
       </c>
       <c r="B40">
-        <f t="shared" si="0"/>
-        <v>3.8593803021701831E-2</v>
+        <v>0</v>
       </c>
       <c r="C40">
-        <f>'Table MV-1'!J48/'Table MV-1'!$J$61</f>
-        <v>3.8593803021701831E-2</v>
+        <v>0</v>
       </c>
       <c r="D40">
         <v>0</v>
@@ -7295,15 +7211,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="B41">
-        <f t="shared" si="0"/>
-        <v>2.8426879307146095E-3</v>
+        <v>0</v>
       </c>
       <c r="C41">
-        <f>'Table MV-1'!J49/'Table MV-1'!$J$61</f>
-        <v>2.8426879307146095E-3</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -7320,15 +7234,13 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>146</v>
       </c>
       <c r="B42">
-        <f t="shared" si="0"/>
-        <v>1.6494772704388254E-2</v>
+        <v>0</v>
       </c>
       <c r="C42">
-        <f>'Table MV-1'!J50/'Table MV-1'!$J$61</f>
-        <v>1.6494772704388254E-2</v>
+        <v>0</v>
       </c>
       <c r="D42">
         <v>0</v>
@@ -7345,15 +7257,13 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>147</v>
       </c>
       <c r="B43">
-        <f t="shared" si="0"/>
-        <v>5.1835093488657516E-3</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <f>'Table MV-1'!J51/'Table MV-1'!$J$61</f>
-        <v>5.1835093488657516E-3</v>
+        <v>0</v>
       </c>
       <c r="D43">
         <v>0</v>
@@ -7370,15 +7280,13 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44" t="s">
-        <v>16</v>
+        <v>148</v>
       </c>
       <c r="B44">
-        <f t="shared" si="0"/>
-        <v>2.1883288976798098E-2</v>
+        <v>0</v>
       </c>
       <c r="C44">
-        <f>'Table MV-1'!J52/'Table MV-1'!$J$61</f>
-        <v>2.1883288976798098E-2</v>
+        <v>0</v>
       </c>
       <c r="D44">
         <v>0</v>
@@ -7395,15 +7303,13 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45" t="s">
-        <v>15</v>
+        <v>149</v>
       </c>
       <c r="B45">
-        <f t="shared" si="0"/>
-        <v>8.6297781225124395E-2</v>
+        <v>0</v>
       </c>
       <c r="C45">
-        <f>'Table MV-1'!J53/'Table MV-1'!$J$61</f>
-        <v>8.6297781225124395E-2</v>
+        <v>0</v>
       </c>
       <c r="D45">
         <v>0</v>
@@ -7420,15 +7326,13 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46" t="s">
-        <v>14</v>
+        <v>150</v>
       </c>
       <c r="B46">
-        <f t="shared" si="0"/>
-        <v>8.9600234207263124E-3</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <f>'Table MV-1'!J54/'Table MV-1'!$J$61</f>
-        <v>8.9600234207263124E-3</v>
+        <v>0</v>
       </c>
       <c r="D46">
         <v>0</v>
@@ -7445,15 +7349,13 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47" t="s">
-        <v>13</v>
+        <v>151</v>
       </c>
       <c r="B47">
-        <f t="shared" si="0"/>
-        <v>2.3814053188992734E-3</v>
+        <v>0</v>
       </c>
       <c r="C47">
-        <f>'Table MV-1'!J55/'Table MV-1'!$J$61</f>
-        <v>2.3814053188992734E-3</v>
+        <v>0</v>
       </c>
       <c r="D47">
         <v>0</v>
@@ -7470,15 +7372,13 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>12</v>
+        <v>152</v>
       </c>
       <c r="B48">
-        <f t="shared" si="0"/>
-        <v>2.6816184066770478E-2</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <f>'Table MV-1'!J56/'Table MV-1'!$J$61</f>
-        <v>2.6816184066770478E-2</v>
+        <v>0</v>
       </c>
       <c r="D48">
         <v>0</v>
@@ -7495,15 +7395,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="B49">
-        <f t="shared" si="0"/>
-        <v>2.6086002141878541E-2</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <f>'Table MV-1'!J57/'Table MV-1'!$J$61</f>
-        <v>2.6086002141878541E-2</v>
+        <v>0</v>
       </c>
       <c r="D49">
         <v>0</v>
@@ -7520,15 +7418,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50" t="s">
-        <v>10</v>
+        <v>154</v>
       </c>
       <c r="B50">
-        <f t="shared" si="0"/>
-        <v>6.8260176103406393E-3</v>
+        <v>0</v>
       </c>
       <c r="C50">
-        <f>'Table MV-1'!J58/'Table MV-1'!$J$61</f>
-        <v>6.8260176103406393E-3</v>
+        <v>0</v>
       </c>
       <c r="D50">
         <v>0</v>
@@ -7545,15 +7441,13 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51" t="s">
-        <v>9</v>
+        <v>155</v>
       </c>
       <c r="B51">
-        <f t="shared" si="0"/>
-        <v>2.1205726135675299E-2</v>
+        <v>0</v>
       </c>
       <c r="C51">
-        <f>'Table MV-1'!J59/'Table MV-1'!$J$61</f>
-        <v>2.1205726135675299E-2</v>
+        <v>0</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -7570,15 +7464,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" t="s">
-        <v>8</v>
+        <v>156</v>
       </c>
       <c r="B52">
-        <f t="shared" si="0"/>
-        <v>3.9463197884523288E-3</v>
+        <v>0</v>
       </c>
       <c r="C52">
-        <f>'Table MV-1'!J60/'Table MV-1'!$J$61</f>
-        <v>3.9463197884523288E-3</v>
+        <v>0</v>
       </c>
       <c r="D52">
         <v>0</v>
@@ -7595,7 +7487,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -7618,7 +7510,7 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -7641,7 +7533,7 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B55">
         <v>0</v>
@@ -7664,7 +7556,7 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -7687,7 +7579,7 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -7710,7 +7602,7 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B58">
         <v>0</v>
@@ -7733,7 +7625,7 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B59">
         <v>0</v>
@@ -7756,7 +7648,7 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -7779,7 +7671,7 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B61">
         <v>0</v>
@@ -7806,6 +7698,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A251C7805F896F47A4F48569C73A0799" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="7abd873f26c83d98889b6bc5171c7cdd">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="f3083de3-5d4e-49f2-a3cd-0aeb079e6739" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="295384f30983e71c631053ca9b14fb23" ns2:_="">
     <xsd:import namespace="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
@@ -7949,38 +7850,43 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{486479BA-9C82-45F5-BBDB-D421DBACC914}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51AC19AA-12F7-4F25-8EDB-0507AFD1E7C2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{52FEB56B-A555-4C09-8755-A4675828AB41}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f3083de3-5d4e-49f2-a3cd-0aeb079e6739"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FE45BD7-ED0B-409C-A575-E37A6B341E54}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51AC19AA-12F7-4F25-8EDB-0507AFD1E7C2}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>